--- a/reports/2026-03-13.xlsx
+++ b/reports/2026-03-13.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-13 13:59 UTC</t>
+          <t>2026-03-13 14:28 UTC</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-13_1773410268225</t>
+          <t>2026-03-13_1773412030547</t>
         </is>
       </c>
     </row>
@@ -960,10 +960,10 @@
         <v>0.110200414416488</v>
       </c>
       <c r="P2" t="n">
-        <v>0.13488</v>
+        <v>0.13284</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.39518400560523</v>
+        <v>20.5440112937767</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -992,22 +992,22 @@
         <v>2.042157278246345</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.304052801364525</v>
+        <v>0.3242957879256485</v>
       </c>
       <c r="AA2" t="n">
-        <v>2632.9426869</v>
+        <v>4909.629529299999</v>
       </c>
       <c r="AB2" t="n">
-        <v>2546.703558</v>
+        <v>1823.8426701</v>
       </c>
       <c r="AC2" t="n">
-        <v>104.745549</v>
+        <v>126.802927</v>
       </c>
       <c r="AD2" t="n">
-        <v>2029.938666</v>
+        <v>2439.349938</v>
       </c>
       <c r="AE2" t="n">
-        <v>134672343.3792853</v>
+        <v>132957042.9929349</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1066,12 +1066,12 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N3" t="b">
@@ -1081,10 +1081,10 @@
         <v>189.1301506579593</v>
       </c>
       <c r="P3" t="n">
-        <v>246</v>
+        <v>248.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>30.06916091601362</v>
+        <v>31.64479546694743</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1113,22 +1113,22 @@
         <v>0.7222300558129753</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.06101157186146536</v>
+        <v>0.04418646689028245</v>
       </c>
       <c r="AA3" t="n">
-        <v>183436.9936</v>
+        <v>155316.71448</v>
       </c>
       <c r="AB3" t="n">
-        <v>159550.69238</v>
+        <v>165852.81793</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.817585</v>
+        <v>4.460736</v>
       </c>
       <c r="AD3" t="n">
-        <v>8.298085</v>
+        <v>7.727379</v>
       </c>
       <c r="AE3" t="n">
-        <v>2648903687.388114</v>
+        <v>2676695551.010193</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -1198,10 +1198,10 @@
         <v>1.147927547711516e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.289e-08</v>
+        <v>1.292e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.28931674039213</v>
+        <v>12.5506572758624</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1230,22 +1230,22 @@
         <v>0.9363583107028461</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3880481179666185</v>
+        <v>0.3871467286101467</v>
       </c>
       <c r="AA4" t="n">
-        <v>9248.929758850451</v>
+        <v>7252.094326413981</v>
       </c>
       <c r="AB4" t="n">
-        <v>2778.37937073751</v>
+        <v>3121.73785897156</v>
       </c>
       <c r="AC4" t="n">
-        <v>90.065788</v>
+        <v>84.65194</v>
       </c>
       <c r="AD4" t="n">
-        <v>2587.200892</v>
+        <v>2924.24184</v>
       </c>
       <c r="AE4" t="n">
-        <v>27094344.61463413</v>
+        <v>27115789.93960047</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
         <v>0.0009970523542217533</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0011537</v>
+        <v>0.0011457</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.71107526249387</v>
+        <v>14.90871017442943</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1347,22 +1347,22 @@
         <v>1.724620090110486</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1385881333910818</v>
+        <v>0.113482606608187</v>
       </c>
       <c r="AA5" t="n">
-        <v>12392.024213712</v>
+        <v>8771.051844965999</v>
       </c>
       <c r="AB5" t="n">
-        <v>9784.299107205999</v>
+        <v>7862.599339398</v>
       </c>
       <c r="AC5" t="n">
-        <v>34.35874</v>
+        <v>33.541896</v>
       </c>
       <c r="AD5" t="n">
-        <v>147.503272</v>
+        <v>206.358177</v>
       </c>
       <c r="AE5" t="n">
-        <v>79794508.20394301</v>
+        <v>78926093.98436658</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         <v>3.798455337233129</v>
       </c>
       <c r="P6" t="n">
-        <v>4.232</v>
+        <v>4.222</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.41370963394488</v>
+        <v>11.15044472460191</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>0.3077287252929317</v>
       </c>
       <c r="AA6" t="n">
-        <v>2516.6242476</v>
+        <v>1567.9446499</v>
       </c>
       <c r="AB6" t="n">
-        <v>1179.3623385</v>
+        <v>821.0137173999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>127.143684</v>
+        <v>119.806795</v>
       </c>
       <c r="AD6" t="n">
-        <v>1509.444509</v>
+        <v>1311.874591</v>
       </c>
       <c r="AE6" t="n">
-        <v>28819343.64610516</v>
+        <v>28746139.14139889</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
         <v>0.02900106765561269</v>
       </c>
       <c r="P7" t="n">
-        <v>0.035047</v>
+        <v>0.035104</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.84727505960358</v>
+        <v>21.04381954781649</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1585,22 +1585,22 @@
         <v>0.7732521922222566</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.05992210126835168</v>
+        <v>0.03979873212610548</v>
       </c>
       <c r="AA7" t="n">
-        <v>31456.85675032</v>
+        <v>29872.01766984</v>
       </c>
       <c r="AB7" t="n">
-        <v>30911.96604291</v>
+        <v>26116.93991756</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.585378</v>
+        <v>39.90953</v>
       </c>
       <c r="AD7" t="n">
-        <v>48.821403</v>
+        <v>60.251329</v>
       </c>
       <c r="AE7" t="n">
-        <v>173506421.7746619</v>
+        <v>172888865.9912609</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1655,12 +1655,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N8" t="b">
@@ -1670,10 +1670,10 @@
         <v>1.445847009477454</v>
       </c>
       <c r="P8" t="n">
-        <v>1.921</v>
+        <v>1.923</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.8632965595905</v>
+        <v>33.00162378141205</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1702,22 +1702,22 @@
         <v>0.7725599901087858</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.05217845030003193</v>
+        <v>0.05206977349649112</v>
       </c>
       <c r="AA8" t="n">
-        <v>61772.65783</v>
+        <v>92217.17320999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>176471.09527</v>
+        <v>191081.68535</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.651571</v>
+        <v>5.518982</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.418569</v>
+        <v>12.165559</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000609724.289852</v>
+        <v>999402407.8363203</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         <v>14.79753816275856</v>
       </c>
       <c r="P9" t="n">
-        <v>20.5628</v>
+        <v>20.381</v>
       </c>
       <c r="Q9" t="n">
-        <v>38.96095265191515</v>
+        <v>37.73236991064848</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1819,22 +1819,22 @@
         <v>1.109681910964214</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1231308325931591</v>
+        <v>0.03135902159852268</v>
       </c>
       <c r="AA9" t="n">
-        <v>12141.355734</v>
+        <v>11939.658028</v>
       </c>
       <c r="AB9" t="n">
-        <v>10953.932134</v>
+        <v>13682.418884</v>
       </c>
       <c r="AC9" t="n">
-        <v>40.208095</v>
+        <v>25.775688</v>
       </c>
       <c r="AD9" t="n">
-        <v>105.518971</v>
+        <v>84.913076</v>
       </c>
       <c r="AE9" t="n">
-        <v>403198901.803517</v>
+        <v>399024345.6702442</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1889,12 +1889,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N10" t="b">
@@ -1904,10 +1904,10 @@
         <v>0.1642781757748225</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1829</v>
+        <v>0.1827</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.33554359083129</v>
+        <v>11.21379887394685</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1936,22 +1936,22 @@
         <v>1.771005290154004</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.05462988254576167</v>
+        <v>0.05471956224349602</v>
       </c>
       <c r="AA10" t="n">
-        <v>114744.404657</v>
+        <v>134026.505591</v>
       </c>
       <c r="AB10" t="n">
-        <v>98881.89181500001</v>
+        <v>87370.85380300001</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.518551</v>
+        <v>13.738244</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.075354</v>
+        <v>20.797632</v>
       </c>
       <c r="AE10" t="n">
-        <v>416044104.6401608</v>
+        <v>413456127.4331153</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         <v>0.02636535704458694</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0276</v>
+        <v>0.02756</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.682822816793752</v>
+        <v>4.531108580827392</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2057,22 +2057,22 @@
         <v>0.9748827879364741</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.03622532149972683</v>
+        <v>0.07254261878853531</v>
       </c>
       <c r="AA11" t="n">
-        <v>19176.1775736</v>
+        <v>17429.5337402</v>
       </c>
       <c r="AB11" t="n">
-        <v>5504.6689823</v>
+        <v>9052.3502816</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.350011</v>
+        <v>17.549545</v>
       </c>
       <c r="AD11" t="n">
-        <v>2238.589311</v>
+        <v>892.559546</v>
       </c>
       <c r="AE11" t="n">
-        <v>296776086.4414722</v>
+        <v>296836070.7969016</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
         <v>0.05036933866812346</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0574</v>
+        <v>0.05692</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.95821648205586</v>
+        <v>13.00525578673552</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2178,22 +2178,22 @@
         <v>0.7505418108402893</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1569995638901</v>
+        <v>0.1230552869825096</v>
       </c>
       <c r="AA12" t="n">
-        <v>5425.7208069</v>
+        <v>4547.9046176</v>
       </c>
       <c r="AB12" t="n">
-        <v>7210.5853054</v>
+        <v>8890.1536394</v>
       </c>
       <c r="AC12" t="n">
-        <v>37.292672</v>
+        <v>26.136313</v>
       </c>
       <c r="AD12" t="n">
-        <v>1749.788006</v>
+        <v>1459.049458</v>
       </c>
       <c r="AE12" t="n">
-        <v>56737209.79061349</v>
+        <v>56378578.42868812</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N13" t="b">
@@ -2267,10 +2267,10 @@
         <v>0.04632072944300417</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04957</v>
+        <v>0.04908</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.014722341525137</v>
+        <v>5.956880623805794</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2299,22 +2299,22 @@
         <v>1.188646740138043</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.1008776354282285</v>
+        <v>0.06109357499235375</v>
       </c>
       <c r="AA13" t="n">
-        <v>48514.3572597</v>
+        <v>88393.5476339</v>
       </c>
       <c r="AB13" t="n">
-        <v>44309.403469</v>
+        <v>51498.6801845</v>
       </c>
       <c r="AC13" t="n">
-        <v>26.40713</v>
+        <v>19.337745</v>
       </c>
       <c r="AD13" t="n">
-        <v>35.208451</v>
+        <v>30.440502</v>
       </c>
       <c r="AE13" t="n">
-        <v>49678174.26001582</v>
+        <v>49197833.63023981</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_late</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2384,14 +2384,14 @@
         <v>0.0285777102898215</v>
       </c>
       <c r="P14" t="n">
-        <v>0.029009</v>
+        <v>0.029694</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.509182176614443</v>
+        <v>3.906155177785853</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -2416,22 +2416,22 @@
         <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1309577144432569</v>
+        <v>0.14143795251726</v>
       </c>
       <c r="AA14" t="n">
-        <v>16396.78619624</v>
+        <v>17683.23305259</v>
       </c>
       <c r="AB14" t="n">
-        <v>16353.00053977</v>
+        <v>15857.18866089</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.605772</v>
+        <v>17.922057</v>
       </c>
       <c r="AD14" t="n">
-        <v>56.346388</v>
+        <v>61.456725</v>
       </c>
       <c r="AE14" t="n">
-        <v>603824415.0910628</v>
+        <v>617219779.7654667</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N15" t="b">
@@ -2505,10 +2505,10 @@
         <v>6.052618123397238e-06</v>
       </c>
       <c r="P15" t="n">
-        <v>6.505e-06</v>
+        <v>6.436e-06</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.474151968286535</v>
+        <v>6.33414943395727</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2537,22 +2537,22 @@
         <v>0.9823643455186037</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.1844167819271562</v>
+        <v>0.0621310966138599</v>
       </c>
       <c r="AA15" t="n">
-        <v>143641.672286313</v>
+        <v>107175.784835942</v>
       </c>
       <c r="AB15" t="n">
-        <v>128778.043071605</v>
+        <v>131444.314707715</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.220839</v>
+        <v>3.106555</v>
       </c>
       <c r="AD15" t="n">
-        <v>15.692354</v>
+        <v>6.580429</v>
       </c>
       <c r="AE15" t="n">
-        <v>573879081.124169</v>
+        <v>567597784.2616116</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
         <v>0.05806474404916181</v>
       </c>
       <c r="P16" t="n">
-        <v>0.07002</v>
+        <v>0.0707</v>
       </c>
       <c r="Q16" t="n">
-        <v>20.58952665100187</v>
+        <v>21.76063316517898</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2654,22 +2654,22 @@
         <v>0.8902070838097473</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.09985022466300636</v>
+        <v>0.254596888260254</v>
       </c>
       <c r="AA16" t="n">
-        <v>7397.474058</v>
+        <v>6564.195738500001</v>
       </c>
       <c r="AB16" t="n">
-        <v>5651.599098</v>
+        <v>5734.8358838</v>
       </c>
       <c r="AC16" t="n">
-        <v>43.173125</v>
+        <v>37.081412</v>
       </c>
       <c r="AD16" t="n">
-        <v>380.582406</v>
+        <v>303.508053</v>
       </c>
       <c r="AE16" t="n">
-        <v>41922982.35535531</v>
+        <v>42453769.25442257</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         <v>0.01117927153331177</v>
       </c>
       <c r="P17" t="n">
-        <v>0.01432</v>
+        <v>0.014349</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.09421398639032</v>
+        <v>28.35362265996611</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2771,22 +2771,22 @@
         <v>1.633947238596579</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.09068396637718151</v>
+        <v>0.1601727079633723</v>
       </c>
       <c r="AA17" t="n">
-        <v>11314.58276114</v>
+        <v>10324.50881124</v>
       </c>
       <c r="AB17" t="n">
-        <v>9123.347688940001</v>
+        <v>7322.67044618</v>
       </c>
       <c r="AC17" t="n">
-        <v>31.81632</v>
+        <v>19.683279</v>
       </c>
       <c r="AD17" t="n">
-        <v>200.113472</v>
+        <v>130.56215</v>
       </c>
       <c r="AE17" t="n">
-        <v>46490855.46455152</v>
+        <v>46755087.47055912</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | rebound_not_confirmed</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | rebound_not_confirmed | entry_late</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2860,14 +2860,14 @@
         <v>0.2885135322309713</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2892</v>
+        <v>0.2904</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2379326070845122</v>
+        <v>0.6538576386491579</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>at_trigger</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2892,22 +2892,22 @@
         <v>2.112894001739067</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.03458412588621441</v>
+        <v>0.03445305770886787</v>
       </c>
       <c r="AA18" t="n">
-        <v>641825.068681</v>
+        <v>564904.779236</v>
       </c>
       <c r="AB18" t="n">
-        <v>501079.618378</v>
+        <v>555504.689427</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.306465</v>
+        <v>4.295596</v>
       </c>
       <c r="AD18" t="n">
-        <v>7.082438</v>
+        <v>6.094814</v>
       </c>
       <c r="AE18" t="n">
-        <v>27407013250.7598</v>
+        <v>27515654442.7241</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         <v>2.47809057249777</v>
       </c>
       <c r="P19" t="n">
-        <v>2.664</v>
+        <v>2.679</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.5021239968176</v>
+        <v>8.107428749051904</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -3009,22 +3009,22 @@
         <v>0.8751587448786063</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.0375445841937426</v>
+        <v>0.03732039559620579</v>
       </c>
       <c r="AA19" t="n">
-        <v>26702.42017</v>
+        <v>33343.19253</v>
       </c>
       <c r="AB19" t="n">
-        <v>27606.54192</v>
+        <v>31672.9859</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.73138</v>
+        <v>6.445681</v>
       </c>
       <c r="AD19" t="n">
-        <v>27.85864</v>
+        <v>19.359038</v>
       </c>
       <c r="AE19" t="n">
-        <v>1465810368.071437</v>
+        <v>1468397749.983756</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -3094,10 +3094,10 @@
         <v>0.2489011953145036</v>
       </c>
       <c r="P20" t="n">
-        <v>0.26962</v>
+        <v>0.27214</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.324108150351339</v>
+        <v>9.336558089298297</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3126,22 +3126,22 @@
         <v>1.262706997713724</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.08542722900066947</v>
+        <v>0.07716191141077251</v>
       </c>
       <c r="AA20" t="n">
-        <v>23097.3329695</v>
+        <v>23289.6543774</v>
       </c>
       <c r="AB20" t="n">
-        <v>23370.4439224</v>
+        <v>18821.2035902</v>
       </c>
       <c r="AC20" t="n">
-        <v>12.907485</v>
+        <v>21.789848</v>
       </c>
       <c r="AD20" t="n">
-        <v>32.303579</v>
+        <v>57.313014</v>
       </c>
       <c r="AE20" t="n">
-        <v>2619450247.956311</v>
+        <v>2652454659.951961</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
         <v>0.6843957588858424</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.7764</v>
       </c>
       <c r="Q21" t="n">
-        <v>13.77919718083578</v>
+        <v>13.44313431514177</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -3243,22 +3243,22 @@
         <v>0.5366901352912198</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.01283944276818245</v>
+        <v>0.06436248954110264</v>
       </c>
       <c r="AA21" t="n">
-        <v>26463.455126</v>
+        <v>5333.259599</v>
       </c>
       <c r="AB21" t="n">
-        <v>14069.168891</v>
+        <v>7008.372896</v>
       </c>
       <c r="AC21" t="n">
-        <v>11.479924</v>
+        <v>14.204777</v>
       </c>
       <c r="AD21" t="n">
-        <v>86.04649000000001</v>
+        <v>177.571042</v>
       </c>
       <c r="AE21" t="n">
-        <v>512805389.1513671</v>
+        <v>510999516.9457357</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         <v>0.110200414416488</v>
       </c>
       <c r="P2" t="n">
-        <v>0.13488</v>
+        <v>0.13284</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.39518400560523</v>
+        <v>20.5440112937767</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -3798,22 +3798,22 @@
         <v>2.042157278246345</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.304052801364525</v>
+        <v>0.3242957879256485</v>
       </c>
       <c r="AA2" t="n">
-        <v>2632.9426869</v>
+        <v>4909.629529299999</v>
       </c>
       <c r="AB2" t="n">
-        <v>2546.703558</v>
+        <v>1823.8426701</v>
       </c>
       <c r="AC2" t="n">
-        <v>104.745549</v>
+        <v>126.802927</v>
       </c>
       <c r="AD2" t="n">
-        <v>2029.938666</v>
+        <v>2439.349938</v>
       </c>
       <c r="AE2" t="n">
-        <v>134672343.3792853</v>
+        <v>132957042.9929349</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>

--- a/reports/2026-03-13.xlsx
+++ b/reports/2026-03-13.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trade Candidates'!$A$1:$AG$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AG$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AG$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AG$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-13 17:14 UTC</t>
+          <t>2026-03-13 18:12 UTC</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-13_1773422011005</t>
+          <t>2026-03-13_1773425478497</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6.1.1</t>
+          <t>6.2.0</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TAOUSDT</t>
+          <t>TURBOUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Turbo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>92.86</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>92.86</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -941,25 +941,25 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>189.1301506579593</v>
+        <v>0.0009970523542217533</v>
       </c>
       <c r="P2" t="n">
-        <v>238.06</v>
+        <v>0.0011089</v>
       </c>
       <c r="Q2" t="n">
-        <v>25.87099368970001</v>
+        <v>11.21783076933298</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -967,43 +967,43 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>143</v>
+        <v>0.000876</v>
       </c>
       <c r="T2" t="n">
-        <v>24.39069101223599</v>
+        <v>12.14102285694319</v>
       </c>
       <c r="U2" t="n">
-        <v>205.7884413001387</v>
+        <v>0.001118104708443507</v>
       </c>
       <c r="V2" t="n">
-        <v>222.4467319423181</v>
+        <v>0.00123915706266526</v>
       </c>
       <c r="W2" t="n">
-        <v>239.1050225844976</v>
+        <v>0.001360209416887013</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3611150279064879</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7222300558129753</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01680813513740316</v>
+        <v>0.1890444254399879</v>
       </c>
       <c r="AA2" t="n">
-        <v>272406.06689</v>
+        <v>13033.819239434</v>
       </c>
       <c r="AB2" t="n">
-        <v>179499.82512</v>
+        <v>13718.549786779</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.030527</v>
+        <v>37.330736</v>
       </c>
       <c r="AD2" t="n">
-        <v>9.577254999999999</v>
+        <v>91.983525</v>
       </c>
       <c r="AE2" t="n">
-        <v>2561982739.484887</v>
+        <v>76890658.25972548</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SATSUSDT</t>
+          <t>GRTUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SATS (Ordinals)</t>
+          <t>The Graph</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1047,15 +1047,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>92.54000000000001</v>
+        <v>72.67</v>
       </c>
       <c r="I3" t="n">
-        <v>92.54000000000001</v>
+        <v>72.67</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>none</t>
@@ -1067,16 +1071,16 @@
         </is>
       </c>
       <c r="N3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.147927547711516e-08</v>
+        <v>0.02636535704458694</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28e-08</v>
+        <v>0.02716</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.50529513398133</v>
+        <v>3.0139662211637</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1084,43 +1088,43 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>9.19e-09</v>
+        <v>0.02261</v>
       </c>
       <c r="T3" t="n">
-        <v>19.94268263427435</v>
+        <v>14.24352812001062</v>
       </c>
       <c r="U3" t="n">
-        <v>1.255106653635766e-08</v>
+        <v>0.03012071408917389</v>
       </c>
       <c r="V3" t="n">
-        <v>1.362285759560016e-08</v>
+        <v>0.03387607113376083</v>
       </c>
       <c r="W3" t="n">
-        <v>1.469464865484266e-08</v>
+        <v>0.03763142817834778</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4681791553514231</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9363583107028461</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3127443315089968</v>
+        <v>0.03679852805887614</v>
       </c>
       <c r="AA3" t="n">
-        <v>3415.22355819954</v>
+        <v>22930.7515838</v>
       </c>
       <c r="AB3" t="n">
-        <v>3616.39161104171</v>
+        <v>9392.7961254</v>
       </c>
       <c r="AC3" t="n">
-        <v>65.49446</v>
+        <v>16.530536</v>
       </c>
       <c r="AD3" t="n">
-        <v>318.446631</v>
+        <v>894.595982</v>
       </c>
       <c r="AE3" t="n">
-        <v>26865796.25636069</v>
+        <v>291946629.5535995</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -1135,39 +1139,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RENDERUSDT</t>
+          <t>STABLEUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>92.2</v>
+        <v>71.58</v>
       </c>
       <c r="I4" t="n">
-        <v>92.2</v>
+        <v>71.58</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1175,25 +1179,25 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.445847009477454</v>
+        <v>0.02875326170396724</v>
       </c>
       <c r="P4" t="n">
-        <v>1.815</v>
+        <v>0.030698</v>
       </c>
       <c r="Q4" t="n">
-        <v>25.5319538030488</v>
+        <v>6.763539789172635</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1201,43 +1205,43 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1.125</v>
+        <v>0.02653347358497346</v>
       </c>
       <c r="T4" t="n">
-        <v>22.19093772538297</v>
+        <v>7.720126300271171</v>
       </c>
       <c r="U4" t="n">
-        <v>1.569783790711621</v>
+        <v>0.03097304982296101</v>
       </c>
       <c r="V4" t="n">
-        <v>1.693720571945789</v>
+        <v>0.03319283794195478</v>
       </c>
       <c r="W4" t="n">
-        <v>1.817657353179957</v>
+        <v>0.03541262606094855</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3862799950543929</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7725599901087858</v>
+        <v>1.999999999999998</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05499037668407423</v>
+        <v>0.1240775811402071</v>
       </c>
       <c r="AA4" t="n">
-        <v>230294.6049</v>
+        <v>13463.8754557</v>
       </c>
       <c r="AB4" t="n">
-        <v>116328.94583</v>
+        <v>16330.44977471</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.634108</v>
+        <v>20.718641</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.253863</v>
+        <v>59.287695</v>
       </c>
       <c r="AE4" t="n">
-        <v>941721576.21254</v>
+        <v>639693416.556029</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1252,22 +1256,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TURBOUSDT</t>
+          <t>ALGOUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turbo</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1281,15 +1285,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>89.98999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>89.98999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>none</t>
@@ -1301,16 +1309,16 @@
         </is>
       </c>
       <c r="N5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0009970523542217533</v>
+        <v>0.08753434961460149</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0011393</v>
+        <v>0.09268</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.26681810397787</v>
+        <v>5.878435617622002</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1318,43 +1326,43 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.000876</v>
+        <v>0.0806</v>
       </c>
       <c r="T5" t="n">
-        <v>12.14102285694319</v>
+        <v>7.921861126668812</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001101437015244757</v>
+        <v>0.09446869922920298</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00120582167626776</v>
+        <v>0.1014030488438045</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001310206337290763</v>
+        <v>0.108337398458406</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8623100450552439</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.724620090110486</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.202206690403974</v>
+        <v>0.2157031924072538</v>
       </c>
       <c r="AA5" t="n">
-        <v>8539.013566515001</v>
+        <v>54918.842105</v>
       </c>
       <c r="AB5" t="n">
-        <v>11044.857227322</v>
+        <v>71539.51196080001</v>
       </c>
       <c r="AC5" t="n">
-        <v>30.658268</v>
+        <v>11.8515</v>
       </c>
       <c r="AD5" t="n">
-        <v>132.776598</v>
+        <v>17.810538</v>
       </c>
       <c r="AE5" t="n">
-        <v>79459082.03065296</v>
+        <v>824875205.3684626</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1369,22 +1377,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASTERUSDT</t>
+          <t>BNBUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_late</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_late</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1398,15 +1406,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>81.29000000000001</v>
+        <v>70.22</v>
       </c>
       <c r="I6" t="n">
-        <v>81.29000000000001</v>
+        <v>70.22</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>direct</t>
@@ -1418,16 +1430,16 @@
         </is>
       </c>
       <c r="N6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6977936206976634</v>
+        <v>637.328595522682</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7055</v>
+        <v>655.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.104392340909</v>
+        <v>2.865304429395898</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1435,43 +1447,43 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.404</v>
+        <v>570.6</v>
       </c>
       <c r="T6" t="n">
-        <v>42.10322536395855</v>
+        <v>10.47004574899969</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7339075633462934</v>
+        <v>704.057191045364</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7700215059949232</v>
+        <v>770.785786568046</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8061354486435532</v>
+        <v>837.514382090728</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1229228278097776</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2458456556195549</v>
+        <v>2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01417333994755708</v>
+        <v>0.001525285419032649</v>
       </c>
       <c r="AA6" t="n">
-        <v>322361.25617</v>
+        <v>103931.197209</v>
       </c>
       <c r="AB6" t="n">
-        <v>254532.44826</v>
+        <v>153328.524605</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.221767</v>
+        <v>0.218807</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.241057</v>
+        <v>0.388793</v>
       </c>
       <c r="AE6" t="n">
-        <v>1747090406.957026</v>
+        <v>89494699373.23842</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1486,12 +1498,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1501,7 +1513,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1515,19 +1527,15 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>79.61</v>
+        <v>92.86</v>
       </c>
       <c r="I7" t="n">
-        <v>79.61</v>
+        <v>92.86</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>direct</t>
@@ -1542,13 +1550,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>9.278395243029014</v>
+        <v>189.1301506579593</v>
       </c>
       <c r="P7" t="n">
-        <v>9.907</v>
+        <v>231.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.774929721206546</v>
+        <v>22.42363218899914</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1556,43 +1564,43 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>7.55</v>
+        <v>143</v>
       </c>
       <c r="T7" t="n">
-        <v>18.62817004187853</v>
+        <v>24.39069101223599</v>
       </c>
       <c r="U7" t="n">
-        <v>9.821603366651665</v>
+        <v>235.2603013159185</v>
       </c>
       <c r="V7" t="n">
-        <v>10.36481149027431</v>
+        <v>281.3904519738778</v>
       </c>
       <c r="W7" t="n">
-        <v>10.90801961389697</v>
+        <v>327.5206026318371</v>
       </c>
       <c r="X7" t="n">
-        <v>0.31428466712896</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6285693342579191</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01009234495636294</v>
+        <v>0.04755008969675373</v>
       </c>
       <c r="AA7" t="n">
-        <v>738417.4274800001</v>
+        <v>256764.79477</v>
       </c>
       <c r="AB7" t="n">
-        <v>786190.43421</v>
+        <v>252609.78159</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.954283</v>
+        <v>3.372523</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.394731</v>
+        <v>6.058589</v>
       </c>
       <c r="AE7" t="n">
-        <v>4272423740.283321</v>
+        <v>2505676233.001959</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1607,12 +1615,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEEPUSDT</t>
+          <t>SATSUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DeepBook Protocol</t>
+          <t>SATS (Ordinals)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1636,10 +1644,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>78.37</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>78.37</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1659,13 +1667,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02900106765561269</v>
+        <v>1.147927547711516e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>0.034525</v>
+        <v>1.269e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.04734132544337</v>
+        <v>10.54704650392366</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1673,43 +1681,43 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.021229</v>
+        <v>9.19e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>26.79924666190189</v>
+        <v>19.94268263427435</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0320059518320138</v>
+        <v>1.376855095423032e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0350108360084149</v>
+        <v>1.605782643134547e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03801572018481601</v>
+        <v>1.834710190846063e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3866260961111279</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.7732521922222566</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03766423780620047</v>
+        <v>0.3941663381947086</v>
       </c>
       <c r="AA8" t="n">
-        <v>30569.97189791</v>
+        <v>3293.5600946929</v>
       </c>
       <c r="AB8" t="n">
-        <v>29979.23508051</v>
+        <v>5921.88992513072</v>
       </c>
       <c r="AC8" t="n">
-        <v>39.590906</v>
+        <v>66.68345100000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>52.997151</v>
+        <v>1184.483137</v>
       </c>
       <c r="AE8" t="n">
-        <v>170238953.3321181</v>
+        <v>26641246.9796076</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -1724,12 +1732,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VIRTUALUSDT</t>
+          <t>RENDERUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Virtuals Protocol</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1739,7 +1747,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1753,10 +1761,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>74.19</v>
+        <v>92.2</v>
       </c>
       <c r="I9" t="n">
-        <v>74.19</v>
+        <v>92.2</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1764,25 +1772,25 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6843957588858424</v>
+        <v>1.445847009477454</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7513</v>
+        <v>1.798</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.775665650394139</v>
+        <v>24.35617241756571</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1790,43 +1798,43 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.4617</v>
+        <v>1.125</v>
       </c>
       <c r="T9" t="n">
-        <v>32.53903256916414</v>
+        <v>22.19093772538297</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7441550673684542</v>
+        <v>1.766694018954908</v>
       </c>
       <c r="V9" t="n">
-        <v>0.803914375851066</v>
+        <v>2.087541028432361</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8636736843336779</v>
+        <v>2.408388037909815</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2683450676456099</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5366901352912198</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01332178778391913</v>
+        <v>0.05550929780738895</v>
       </c>
       <c r="AA9" t="n">
-        <v>22813.978192</v>
+        <v>188055.69024</v>
       </c>
       <c r="AB9" t="n">
-        <v>17465.65169</v>
+        <v>235194.79543</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.351940000000001</v>
+        <v>5.726887</v>
       </c>
       <c r="AD9" t="n">
-        <v>52.916992</v>
+        <v>11.246003</v>
       </c>
       <c r="AE9" t="n">
-        <v>492444600.8311584</v>
+        <v>934716039.2807738</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -1841,12 +1849,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OKBUSDT</t>
+          <t>ASTERUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1856,7 +1864,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | entry_late</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1870,10 +1878,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>73.54000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>73.54000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1881,69 +1889,69 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>88.4902972992044</v>
+        <v>0.6977936206976634</v>
       </c>
       <c r="P10" t="n">
-        <v>93.58</v>
+        <v>0.702</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.751707086694746</v>
+        <v>0.6028113725274453</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>60.001</v>
+        <v>0.404</v>
       </c>
       <c r="T10" t="n">
-        <v>32.19482606423625</v>
+        <v>42.10322536395855</v>
       </c>
       <c r="U10" t="n">
-        <v>95.27517476024229</v>
+        <v>0.9915872413953267</v>
       </c>
       <c r="V10" t="n">
-        <v>102.0600522212802</v>
+        <v>1.28538086209299</v>
       </c>
       <c r="W10" t="n">
-        <v>108.8449296823181</v>
+        <v>1.579174482790653</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2381553110903641</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4763106221807282</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1783206889371783</v>
+        <v>0.04273808675831142</v>
       </c>
       <c r="AA10" t="n">
-        <v>31635.318538</v>
+        <v>258932.507203</v>
       </c>
       <c r="AB10" t="n">
-        <v>31400.421468</v>
+        <v>253223.755302</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.271236</v>
+        <v>8.259315000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>23.60287</v>
+        <v>13.678932</v>
       </c>
       <c r="AE10" t="n">
-        <v>1966925741.635539</v>
+        <v>1740790451.481992</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -1958,12 +1966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRTUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Graph</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1973,7 +1981,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1987,10 +1995,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>72.67</v>
+        <v>79.61</v>
       </c>
       <c r="I11" t="n">
-        <v>72.67</v>
+        <v>79.61</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -2002,25 +2010,25 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N11" t="b">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02636535704458694</v>
+        <v>9.278395243029014</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02748</v>
+        <v>9.757</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.227680108894649</v>
+        <v>5.158270847866375</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2028,43 +2036,43 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0.02261</v>
+        <v>7.55</v>
       </c>
       <c r="T11" t="n">
-        <v>14.24352812001062</v>
+        <v>18.62817004187853</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02819587351724884</v>
+        <v>11.00679048605803</v>
       </c>
       <c r="V11" t="n">
-        <v>0.03002638998991074</v>
+        <v>12.73518572908704</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03185690646257264</v>
+        <v>14.46358097211606</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4874413939682366</v>
+        <v>0.9999999999999994</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.9748827879364741</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.03639672429481199</v>
+        <v>0.01024852677427052</v>
       </c>
       <c r="AA11" t="n">
-        <v>18166.9851892</v>
+        <v>643477.29533</v>
       </c>
       <c r="AB11" t="n">
-        <v>11704.1059266</v>
+        <v>515086.39766</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.011066</v>
+        <v>2.521521</v>
       </c>
       <c r="AD11" t="n">
-        <v>552.615257</v>
+        <v>7.542973</v>
       </c>
       <c r="AE11" t="n">
-        <v>295356050.6181768</v>
+        <v>4217069987.245726</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -2079,12 +2087,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BBUSDT</t>
+          <t>DEEPUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BounceBit</t>
+          <t>DeepBook Protocol</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2094,7 +2102,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2108,19 +2116,15 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>72.36</v>
+        <v>78.37</v>
       </c>
       <c r="I12" t="n">
-        <v>72.36</v>
+        <v>78.37</v>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>none</t>
@@ -2135,13 +2139,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02779833649920642</v>
+        <v>0.02900106765561269</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02975</v>
+        <v>0.034248</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.020792416299049</v>
+        <v>18.092204075707</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2149,43 +2153,43 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.0235</v>
+        <v>0.021229</v>
       </c>
       <c r="T12" t="n">
-        <v>15.46256733502427</v>
+        <v>26.79924666190189</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03010883086662716</v>
+        <v>0.03677313531122539</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0324193252340479</v>
+        <v>0.04454520296683808</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03472981960146863</v>
+        <v>0.05231727062245077</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5375322215576444</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.075064443115289</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2689075630252108</v>
+        <v>0.08468760494690762</v>
       </c>
       <c r="AA12" t="n">
-        <v>6620.4093092</v>
+        <v>30339.69783419</v>
       </c>
       <c r="AB12" t="n">
-        <v>3528.5371461</v>
+        <v>29761.07505589</v>
       </c>
       <c r="AC12" t="n">
-        <v>100.173805</v>
+        <v>35.477623</v>
       </c>
       <c r="AD12" t="n">
-        <v>299.0465</v>
+        <v>50.084335</v>
       </c>
       <c r="AE12" t="n">
-        <v>31062864.25395158</v>
+        <v>169118989.4684082</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -2200,12 +2204,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STABLEUSDT</t>
+          <t>VIRTUALUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Virtuals Protocol</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2220,19 +2224,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>71.58</v>
+        <v>74.19</v>
       </c>
       <c r="I13" t="n">
-        <v>71.58</v>
+        <v>74.19</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
@@ -2252,13 +2256,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02875326170396724</v>
+        <v>0.6843957588858424</v>
       </c>
       <c r="P13" t="n">
-        <v>0.030172</v>
+        <v>0.7353</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.934182113457464</v>
+        <v>7.43783701947931</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2266,43 +2270,43 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.02653347358497346</v>
+        <v>0.4617</v>
       </c>
       <c r="T13" t="n">
-        <v>7.720126300271171</v>
+        <v>32.53903256916414</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02986315576346412</v>
+        <v>0.9070915177716847</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03097304982296101</v>
+        <v>1.129787276657527</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03208294388245789</v>
+        <v>1.352483035543369</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.1560450870698333</v>
+        <v>0.01360081604896144</v>
       </c>
       <c r="AA13" t="n">
-        <v>15281.25425739</v>
+        <v>21731.378953</v>
       </c>
       <c r="AB13" t="n">
-        <v>14704.33447441</v>
+        <v>14062.314682</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.85046</v>
+        <v>10.686241</v>
       </c>
       <c r="AD13" t="n">
-        <v>72.13377800000001</v>
+        <v>63.04216</v>
       </c>
       <c r="AE13" t="n">
-        <v>622268409.0609215</v>
+        <v>484349156.8254083</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2317,12 +2321,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ALGOUSDT</t>
+          <t>OKBUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2332,7 +2336,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2346,19 +2350,15 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>70.98999999999999</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>70.98999999999999</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>none</t>
@@ -2373,13 +2373,13 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.08753434961460149</v>
+        <v>88.4902972992044</v>
       </c>
       <c r="P14" t="n">
-        <v>0.09417</v>
+        <v>93.485</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.580624537240666</v>
+        <v>5.644350683903188</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2387,43 +2387,43 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0.0806</v>
+        <v>60.001</v>
       </c>
       <c r="T14" t="n">
-        <v>7.921861126668812</v>
+        <v>32.19482606423625</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09248652430304215</v>
+        <v>116.9795945984088</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0974386989914828</v>
+        <v>145.4688918976132</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1023908736799235</v>
+        <v>173.9581891968176</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7141512850769717</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.428302570153943</v>
+        <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1911639762107048</v>
+        <v>0.135867384873798</v>
       </c>
       <c r="AA14" t="n">
-        <v>54217.6231264</v>
+        <v>30918.753168</v>
       </c>
       <c r="AB14" t="n">
-        <v>72214.39190069999</v>
+        <v>30649.90774</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.659385</v>
+        <v>9.302528000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>25.109853</v>
+        <v>20.444691</v>
       </c>
       <c r="AE14" t="n">
-        <v>836666308.441128</v>
+        <v>1960436765.975906</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LUNCUSDT</t>
+          <t>BBUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Terra Classic</t>
+          <t>BounceBit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2467,15 +2467,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>70.48</v>
+        <v>72.36</v>
       </c>
       <c r="I15" t="n">
-        <v>70.48</v>
+        <v>72.36</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>none</t>
@@ -2490,13 +2494,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.065225292073741e-05</v>
+        <v>0.02779833649920642</v>
       </c>
       <c r="P15" t="n">
-        <v>4.208e-05</v>
+        <v>0.0302</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5120982889838</v>
+        <v>8.639594318394339</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2504,43 +2508,43 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>3e-05</v>
+        <v>0.0235</v>
       </c>
       <c r="T15" t="n">
-        <v>26.2033519802872</v>
+        <v>15.46256733502427</v>
       </c>
       <c r="U15" t="n">
-        <v>4.339062426387198e-05</v>
+        <v>0.03209667299841285</v>
       </c>
       <c r="V15" t="n">
-        <v>4.612899560700656e-05</v>
+        <v>0.03639500949761927</v>
       </c>
       <c r="W15" t="n">
-        <v>4.886736695014114e-05</v>
+        <v>0.04069334599682569</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2570696887795082</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5141393775590164</v>
+        <v>2.000000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0237670825905997</v>
+        <v>0.2329838575470149</v>
       </c>
       <c r="AA15" t="n">
-        <v>20888.4798224302</v>
+        <v>5812.0013142</v>
       </c>
       <c r="AB15" t="n">
-        <v>14155.6492131806</v>
+        <v>2335.9863665</v>
       </c>
       <c r="AC15" t="n">
-        <v>13.470293</v>
+        <v>72.914423</v>
       </c>
       <c r="AD15" t="n">
-        <v>58.924194</v>
+        <v>277.279967</v>
       </c>
       <c r="AE15" t="n">
-        <v>229583663.8760208</v>
+        <v>31872454.60697597</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2555,12 +2559,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>POPCATUSDT</t>
+          <t>LUNCUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Popcat (SOL)</t>
+          <t>Terra Classic</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2570,7 +2574,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_late</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2584,19 +2588,15 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>70.45</v>
+        <v>70.48</v>
       </c>
       <c r="I16" t="n">
-        <v>70.45</v>
+        <v>70.48</v>
       </c>
       <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>none</t>
@@ -2611,57 +2611,57 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.05085232124071982</v>
+        <v>4.065225292073741e-05</v>
       </c>
       <c r="P16" t="n">
-        <v>0.05446</v>
+        <v>4.187e-05</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.094422970787306</v>
+        <v>2.995521752845809</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0.04</v>
+        <v>3e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>21.34085716431341</v>
+        <v>26.2033519802872</v>
       </c>
       <c r="U16" t="n">
-        <v>0.05499339807192526</v>
+        <v>5.130450584147482e-05</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0591344749031307</v>
+        <v>6.195675876221223e-05</v>
       </c>
       <c r="W16" t="n">
-        <v>0.06327555173433613</v>
+        <v>7.260901168294965e-05</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3815844315101351</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.7631688630202702</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.05512172714745475</v>
+        <v>0.04781257470713943</v>
       </c>
       <c r="AA16" t="n">
-        <v>7300.6559223</v>
+        <v>13483.6751742152</v>
       </c>
       <c r="AB16" t="n">
-        <v>8037.7605137</v>
+        <v>14579.0848007146</v>
       </c>
       <c r="AC16" t="n">
-        <v>39.405985</v>
+        <v>12.802863</v>
       </c>
       <c r="AD16" t="n">
-        <v>2539.193402</v>
+        <v>57.778865</v>
       </c>
       <c r="AE16" t="n">
-        <v>53343923.32587899</v>
+        <v>228516148.7280135</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BNBUSDT</t>
+          <t>POPCATUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>Popcat (SOL)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>70.22</v>
+        <v>70.45</v>
       </c>
       <c r="I17" t="n">
-        <v>70.22</v>
+        <v>70.45</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2720,25 +2720,25 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N17" t="b">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>637.328595522682</v>
+        <v>0.05085232124071982</v>
       </c>
       <c r="P17" t="n">
-        <v>662.8</v>
+        <v>0.05347</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.996588989770422</v>
+        <v>5.147609185604041</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2746,43 +2746,43 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>570.6</v>
+        <v>0.04</v>
       </c>
       <c r="T17" t="n">
-        <v>10.47004574899969</v>
+        <v>21.34085716431341</v>
       </c>
       <c r="U17" t="n">
-        <v>663.7996378200357</v>
+        <v>0.06170464248143965</v>
       </c>
       <c r="V17" t="n">
-        <v>690.2706801173894</v>
+        <v>0.07255696372215947</v>
       </c>
       <c r="W17" t="n">
-        <v>716.7417224147431</v>
+        <v>0.0834092849628793</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3966971294691172</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.7933942589382328</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.001509126442157584</v>
+        <v>0.05611147479660011</v>
       </c>
       <c r="AA17" t="n">
-        <v>103675.727804</v>
+        <v>7992.1844209</v>
       </c>
       <c r="AB17" t="n">
-        <v>129190.754754</v>
+        <v>6775.8749953</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.221317</v>
+        <v>28.79382</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.5128549999999999</v>
+        <v>3759.784346</v>
       </c>
       <c r="AE17" t="n">
-        <v>90306311821.72176</v>
+        <v>52499438.40972688</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -2856,10 +2856,10 @@
         <v>0.05036933866812346</v>
       </c>
       <c r="P18" t="n">
-        <v>0.05507</v>
+        <v>0.05471</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.332386440188433</v>
+        <v>8.617665918698192</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2873,37 +2873,37 @@
         <v>24.55727828714073</v>
       </c>
       <c r="U18" t="n">
-        <v>0.05501119158955856</v>
+        <v>0.06273867733624691</v>
       </c>
       <c r="V18" t="n">
-        <v>0.05965304451099365</v>
+        <v>0.07510801600437038</v>
       </c>
       <c r="W18" t="n">
-        <v>0.06429489743242875</v>
+        <v>0.08747735467249385</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3752709054201446</v>
+        <v>0.9999999999999994</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.7505418108402893</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.09080177971488501</v>
+        <v>0.1280058516960787</v>
       </c>
       <c r="AA18" t="n">
-        <v>8834.1124225</v>
+        <v>9838.1608492</v>
       </c>
       <c r="AB18" t="n">
-        <v>9068.1956424</v>
+        <v>7774.3564486</v>
       </c>
       <c r="AC18" t="n">
-        <v>22.960985</v>
+        <v>29.187841</v>
       </c>
       <c r="AD18" t="n">
-        <v>2028.355496</v>
+        <v>2519.027243</v>
       </c>
       <c r="AE18" t="n">
-        <v>54482815.55986823</v>
+        <v>54162231.83924329</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         <v>0.3320392832291859</v>
       </c>
       <c r="P19" t="n">
-        <v>0.364</v>
+        <v>0.354</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.625582991261217</v>
+        <v>6.613891150841944</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2994,37 +2994,37 @@
         <v>18.68432030867987</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3573409950869511</v>
+        <v>0.3940785664583717</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3826427069447162</v>
+        <v>0.4561178496875575</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4079444188024814</v>
+        <v>0.5181571329167434</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4078337230992093</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.8156674461984177</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.02748385323622069</v>
+        <v>0.02823662289989806</v>
       </c>
       <c r="AA19" t="n">
-        <v>104310.113831</v>
+        <v>93832.759211</v>
       </c>
       <c r="AB19" t="n">
-        <v>58416.063958</v>
+        <v>60719.34531500001</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.762698</v>
+        <v>7.255259</v>
       </c>
       <c r="AD19" t="n">
-        <v>26.543853</v>
+        <v>20.61703</v>
       </c>
       <c r="AE19" t="n">
-        <v>323341094.9582617</v>
+        <v>315930700.4928477</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -3098,10 +3098,10 @@
         <v>0.006969915837321193</v>
       </c>
       <c r="P20" t="n">
-        <v>0.007511</v>
+        <v>0.007359</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.763137680680599</v>
+        <v>5.582336598605853</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3115,37 +3115,37 @@
         <v>24.14542552020259</v>
       </c>
       <c r="U20" t="n">
-        <v>0.007553837240500629</v>
+        <v>0.008652831674642387</v>
       </c>
       <c r="V20" t="n">
-        <v>0.008137758643680066</v>
+        <v>0.01033574751196358</v>
       </c>
       <c r="W20" t="n">
-        <v>0.008721680046859501</v>
+        <v>0.01201866334928477</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3469700565115015</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.6939401130230042</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.01332178778392237</v>
+        <v>0.01358787961138845</v>
       </c>
       <c r="AA20" t="n">
-        <v>33282.71031808</v>
+        <v>28049.32203838</v>
       </c>
       <c r="AB20" t="n">
-        <v>24349.50004843</v>
+        <v>30660.25488808</v>
       </c>
       <c r="AC20" t="n">
-        <v>6.770472</v>
+        <v>5.400901</v>
       </c>
       <c r="AD20" t="n">
-        <v>34.015992</v>
+        <v>18.728805</v>
       </c>
       <c r="AE20" t="n">
-        <v>471526458.4132844</v>
+        <v>463893413.9480594</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3219,14 +3219,14 @@
         <v>8.933081770513899</v>
       </c>
       <c r="P21" t="n">
-        <v>9.297000000000001</v>
+        <v>9.144</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.073826243114809</v>
+        <v>2.361091445309449</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -3236,37 +3236,37 @@
         <v>19.84848920074195</v>
       </c>
       <c r="U21" t="n">
-        <v>9.451838858118967</v>
+        <v>10.7061635410278</v>
       </c>
       <c r="V21" t="n">
-        <v>9.970595945724034</v>
+        <v>12.4792453115417</v>
       </c>
       <c r="W21" t="n">
-        <v>10.4893530333291</v>
+        <v>14.2523270820556</v>
       </c>
       <c r="X21" t="n">
-        <v>0.2925736963923067</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5851473927846134</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.04304315075863079</v>
+        <v>0.04374931641692616</v>
       </c>
       <c r="AA21" t="n">
-        <v>1062670.93036</v>
+        <v>1025365.97615</v>
       </c>
       <c r="AB21" t="n">
-        <v>744636.28353</v>
+        <v>1044397.35065</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.043137</v>
+        <v>3.757822</v>
       </c>
       <c r="AD21" t="n">
-        <v>7.037255</v>
+        <v>7.735224</v>
       </c>
       <c r="AE21" t="n">
-        <v>6577077287.687836</v>
+        <v>6476477451.030374</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3709,8 +3709,605 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TURBOUSDT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | entry_chased</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0009970523542217533</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0011089</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>11.21783076933298</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0.000876</v>
+      </c>
+      <c r="T2" t="n">
+        <v>12.14102285694319</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.001118104708443507</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.00123915706266526</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.001360209416887013</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1890444254399879</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>13033.819239434</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>13718.549786779</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>37.330736</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>91.983525</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>76890658.25972548</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GRTUSDT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The Graph</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>72.67</v>
+      </c>
+      <c r="I3" t="n">
+        <v>72.67</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.02636535704458694</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.02716</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.0139662211637</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.02261</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14.24352812001062</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.03012071408917389</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.03387607113376083</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.03763142817834778</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.03679852805887614</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>22930.7515838</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9392.7961254</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>16.530536</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>894.595982</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>291946629.5535995</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>STABLEUSDT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | entry_chased</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>pullback_to_ema</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>71.58</v>
+      </c>
+      <c r="I4" t="n">
+        <v>71.58</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02875326170396724</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.030698</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6.763539789172635</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.02653347358497346</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7.720126300271171</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.03097304982296101</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.03319283794195478</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.03541262606094855</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.999999999999998</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.1240775811402071</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>13463.8754557</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>16330.44977471</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>20.718641</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>59.287695</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>639693416.556029</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ALGOUSDT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Algorand</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>70.98999999999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>70.98999999999999</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.08753434961460149</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.09268</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.878435617622002</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0806</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7.921861126668812</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.09446869922920298</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1014030488438045</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.108337398458406</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.2157031924072538</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>54918.842105</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>71539.51196080001</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11.8515</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>17.810538</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>824875205.3684626</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BNBUSDT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BNB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_late</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="I6" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>DIRECT_OK</t>
+        </is>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>637.328595522682</v>
+      </c>
+      <c r="P6" t="n">
+        <v>655.59</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.865304429395898</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>570.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10.47004574899969</v>
+      </c>
+      <c r="U6" t="n">
+        <v>704.057191045364</v>
+      </c>
+      <c r="V6" t="n">
+        <v>770.785786568046</v>
+      </c>
+      <c r="W6" t="n">
+        <v>837.514382090728</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.001525285419032649</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>103931.197209</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>153328.524605</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.218807</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.388793</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>89494699373.23842</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG1"/>
+  <autoFilter ref="A1:AG6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>